--- a/AAII_Financials/Yearly/YMAT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/YMAT_YR_FIN.xlsx
@@ -1594,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
         <v>2300</v>
@@ -2072,7 +2072,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
